--- a/DÍA 4/Relativos+y+Absolutos.xlsx
+++ b/DÍA 4/Relativos+y+Absolutos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GUSTAVO\Documents\Cursos Udemy\ExcelTotal\DÍA 4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16DDF3C2-F99A-4CE2-9CE4-6A9F9F063B0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3874BBF-C779-4169-B96F-26A344933F8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{89B45AFE-0D51-45C3-8AF8-197F8903360E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="3" xr2:uid="{89B45AFE-0D51-45C3-8AF8-197F8903360E}"/>
   </bookViews>
   <sheets>
     <sheet name="A1" sheetId="1" r:id="rId1"/>
@@ -271,7 +271,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -280,24 +280,23 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -305,14 +304,19 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -890,21 +894,21 @@
         <f>B2+C2</f>
         <v>4</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="11" t="s">
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="K2" s="12" t="s">
+      <c r="K2" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="L2" s="12"/>
-      <c r="M2" s="12"/>
-      <c r="N2" s="13"/>
+      <c r="L2" s="14"/>
+      <c r="M2" s="14"/>
+      <c r="N2" s="15"/>
     </row>
     <row r="3" spans="2:14" ht="26.4" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B3" s="2">
@@ -917,13 +921,13 @@
         <f t="shared" ref="D3:D11" si="0">B3+C3</f>
         <v>8</v>
       </c>
-      <c r="J3" s="14" t="s">
+      <c r="J3" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="K3" s="15"/>
-      <c r="L3" s="15"/>
-      <c r="M3" s="15"/>
-      <c r="N3" s="16"/>
+      <c r="K3" s="16"/>
+      <c r="L3" s="16"/>
+      <c r="M3" s="16"/>
+      <c r="N3" s="17"/>
     </row>
     <row r="4" spans="2:14" ht="18" x14ac:dyDescent="0.35">
       <c r="B4" s="2">
@@ -951,12 +955,12 @@
       <c r="J5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="K5" s="7" t="s">
+      <c r="K5" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="L5" s="7"/>
-      <c r="M5" s="7"/>
-      <c r="N5" s="7"/>
+      <c r="L5" s="18"/>
+      <c r="M5" s="18"/>
+      <c r="N5" s="18"/>
     </row>
     <row r="6" spans="2:14" ht="25.8" x14ac:dyDescent="0.35">
       <c r="B6" s="2">
@@ -969,19 +973,19 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F6" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
-      <c r="I6" s="6"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="19"/>
+      <c r="I6" s="19"/>
       <c r="J6" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="K6" s="7"/>
-      <c r="L6" s="7"/>
-      <c r="M6" s="7"/>
-      <c r="N6" s="7"/>
+      <c r="K6" s="18"/>
+      <c r="L6" s="18"/>
+      <c r="M6" s="18"/>
+      <c r="N6" s="18"/>
     </row>
     <row r="7" spans="2:14" ht="18" x14ac:dyDescent="0.35">
       <c r="B7" s="2">
@@ -994,10 +998,10 @@
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="6"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="19"/>
+      <c r="H7" s="19"/>
+      <c r="I7" s="19"/>
     </row>
     <row r="8" spans="2:14" ht="58.8" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="2">
@@ -1010,10 +1014,10 @@
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="19"/>
+      <c r="H8" s="19"/>
+      <c r="I8" s="19"/>
     </row>
     <row r="9" spans="2:14" ht="25.8" x14ac:dyDescent="0.5">
       <c r="B9" s="2">
@@ -1029,12 +1033,12 @@
       <c r="J9" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="K9" s="7" t="s">
+      <c r="K9" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="L9" s="7"/>
-      <c r="M9" s="7"/>
-      <c r="N9" s="7"/>
+      <c r="L9" s="18"/>
+      <c r="M9" s="18"/>
+      <c r="N9" s="18"/>
     </row>
     <row r="10" spans="2:14" ht="25.8" x14ac:dyDescent="0.35">
       <c r="B10" s="2">
@@ -1050,10 +1054,10 @@
       <c r="J10" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="K10" s="7"/>
-      <c r="L10" s="7"/>
-      <c r="M10" s="7"/>
-      <c r="N10" s="7"/>
+      <c r="K10" s="18"/>
+      <c r="L10" s="18"/>
+      <c r="M10" s="18"/>
+      <c r="N10" s="18"/>
     </row>
     <row r="11" spans="2:14" ht="18" x14ac:dyDescent="0.35">
       <c r="B11" s="2">
@@ -1071,21 +1075,21 @@
       <c r="J12" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="K12" s="7" t="s">
+      <c r="K12" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="L12" s="7"/>
-      <c r="M12" s="7"/>
-      <c r="N12" s="7"/>
+      <c r="L12" s="18"/>
+      <c r="M12" s="18"/>
+      <c r="N12" s="18"/>
     </row>
     <row r="13" spans="2:14" ht="25.8" x14ac:dyDescent="0.3">
       <c r="J13" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="K13" s="7"/>
-      <c r="L13" s="7"/>
-      <c r="M13" s="7"/>
-      <c r="N13" s="7"/>
+      <c r="K13" s="18"/>
+      <c r="L13" s="18"/>
+      <c r="M13" s="18"/>
+      <c r="N13" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -1102,7 +1106,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05E7DFF7-8A9C-4BAC-951B-27C5D286FB18}">
-  <dimension ref="B2:O13"/>
+  <dimension ref="B2:O27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="11" max="11" width="36" bestFit="1" customWidth="1"/>
@@ -1119,24 +1123,24 @@
         <f>$B$2*C2</f>
         <v>3</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="G2" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="9"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="7"/>
       <c r="K2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="L2" s="7" t="s">
+      <c r="L2" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
+      <c r="M2" s="18"/>
+      <c r="N2" s="18"/>
+      <c r="O2" s="18"/>
     </row>
     <row r="3" spans="2:15" ht="25.8" x14ac:dyDescent="0.35">
-      <c r="B3" s="10"/>
+      <c r="B3" s="8"/>
       <c r="C3" s="2">
         <v>2</v>
       </c>
@@ -1147,13 +1151,13 @@
       <c r="K3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="L3" s="7"/>
-      <c r="M3" s="7"/>
-      <c r="N3" s="7"/>
-      <c r="O3" s="7"/>
+      <c r="L3" s="18"/>
+      <c r="M3" s="18"/>
+      <c r="N3" s="18"/>
+      <c r="O3" s="18"/>
     </row>
     <row r="4" spans="2:15" ht="18" x14ac:dyDescent="0.35">
-      <c r="B4" s="10"/>
+      <c r="B4" s="8"/>
       <c r="C4" s="2">
         <v>3</v>
       </c>
@@ -1163,7 +1167,7 @@
       </c>
     </row>
     <row r="5" spans="2:15" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="B5" s="10"/>
+      <c r="B5" s="8"/>
       <c r="C5" s="2">
         <v>4</v>
       </c>
@@ -1171,18 +1175,18 @@
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="K5" s="17" t="s">
+      <c r="K5" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="L5" s="18" t="s">
+      <c r="L5" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="M5" s="18"/>
-      <c r="N5" s="18"/>
-      <c r="O5" s="18"/>
+      <c r="M5" s="20"/>
+      <c r="N5" s="20"/>
+      <c r="O5" s="20"/>
     </row>
     <row r="6" spans="2:15" ht="25.8" x14ac:dyDescent="0.35">
-      <c r="B6" s="10"/>
+      <c r="B6" s="8"/>
       <c r="C6" s="2">
         <v>5</v>
       </c>
@@ -1190,16 +1194,16 @@
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="K6" s="19" t="s">
+      <c r="K6" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="L6" s="18"/>
-      <c r="M6" s="18"/>
-      <c r="N6" s="18"/>
-      <c r="O6" s="18"/>
+      <c r="L6" s="20"/>
+      <c r="M6" s="20"/>
+      <c r="N6" s="20"/>
+      <c r="O6" s="20"/>
     </row>
     <row r="7" spans="2:15" ht="18" x14ac:dyDescent="0.35">
-      <c r="B7" s="10"/>
+      <c r="B7" s="8"/>
       <c r="C7" s="2">
         <v>6</v>
       </c>
@@ -1207,15 +1211,15 @@
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="F7" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="6"/>
+      <c r="G7" s="19"/>
+      <c r="H7" s="19"/>
+      <c r="I7" s="19"/>
     </row>
     <row r="8" spans="2:15" ht="18" x14ac:dyDescent="0.35">
-      <c r="B8" s="10"/>
+      <c r="B8" s="8"/>
       <c r="C8" s="2">
         <v>7</v>
       </c>
@@ -1223,13 +1227,13 @@
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="19"/>
+      <c r="H8" s="19"/>
+      <c r="I8" s="19"/>
     </row>
     <row r="9" spans="2:15" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="B9" s="10"/>
+      <c r="B9" s="8"/>
       <c r="C9" s="2">
         <v>8</v>
       </c>
@@ -1237,22 +1241,22 @@
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="19"/>
+      <c r="I9" s="19"/>
       <c r="K9" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="L9" s="7" t="s">
+      <c r="L9" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="M9" s="7"/>
-      <c r="N9" s="7"/>
-      <c r="O9" s="7"/>
+      <c r="M9" s="18"/>
+      <c r="N9" s="18"/>
+      <c r="O9" s="18"/>
     </row>
     <row r="10" spans="2:15" ht="25.8" x14ac:dyDescent="0.35">
-      <c r="B10" s="10"/>
+      <c r="B10" s="8"/>
       <c r="C10" s="2">
         <v>9</v>
       </c>
@@ -1263,13 +1267,13 @@
       <c r="K10" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="L10" s="7"/>
-      <c r="M10" s="7"/>
-      <c r="N10" s="7"/>
-      <c r="O10" s="7"/>
+      <c r="L10" s="18"/>
+      <c r="M10" s="18"/>
+      <c r="N10" s="18"/>
+      <c r="O10" s="18"/>
     </row>
     <row r="11" spans="2:15" ht="18" x14ac:dyDescent="0.35">
-      <c r="B11" s="10"/>
+      <c r="B11" s="8"/>
       <c r="C11" s="2">
         <v>10</v>
       </c>
@@ -1282,21 +1286,198 @@
       <c r="K12" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="L12" s="7" t="s">
+      <c r="L12" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="M12" s="7"/>
-      <c r="N12" s="7"/>
-      <c r="O12" s="7"/>
-    </row>
-    <row r="13" spans="2:15" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="K13" s="5" t="s">
+      <c r="M12" s="18"/>
+      <c r="N12" s="18"/>
+      <c r="O12" s="18"/>
+    </row>
+    <row r="13" spans="2:15" ht="25.8" x14ac:dyDescent="0.35">
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="21"/>
+      <c r="J13" s="21"/>
+      <c r="K13" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="L13" s="7"/>
-      <c r="M13" s="7"/>
-      <c r="N13" s="7"/>
-      <c r="O13" s="7"/>
+      <c r="L13" s="18"/>
+      <c r="M13" s="18"/>
+      <c r="N13" s="18"/>
+      <c r="O13" s="18"/>
+    </row>
+    <row r="14" spans="2:15" ht="18" x14ac:dyDescent="0.35">
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="21"/>
+      <c r="J14" s="21"/>
+      <c r="K14" s="21"/>
+    </row>
+    <row r="15" spans="2:15" ht="18" x14ac:dyDescent="0.35">
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="21"/>
+      <c r="J15" s="21"/>
+      <c r="K15" s="21"/>
+    </row>
+    <row r="16" spans="2:15" ht="18" x14ac:dyDescent="0.35">
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="21"/>
+      <c r="J16" s="21"/>
+      <c r="K16" s="21"/>
+    </row>
+    <row r="17" spans="2:11" ht="18" x14ac:dyDescent="0.35">
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="21"/>
+      <c r="J17" s="21"/>
+      <c r="K17" s="21"/>
+    </row>
+    <row r="18" spans="2:11" ht="18" x14ac:dyDescent="0.35">
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="21"/>
+      <c r="J18" s="21"/>
+      <c r="K18" s="21"/>
+    </row>
+    <row r="19" spans="2:11" ht="18" x14ac:dyDescent="0.35">
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="21"/>
+      <c r="J19" s="21"/>
+      <c r="K19" s="21"/>
+    </row>
+    <row r="20" spans="2:11" ht="18" x14ac:dyDescent="0.35">
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="21"/>
+      <c r="J20" s="21"/>
+      <c r="K20" s="21"/>
+    </row>
+    <row r="21" spans="2:11" ht="18" x14ac:dyDescent="0.35">
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="21"/>
+      <c r="J21" s="21"/>
+      <c r="K21" s="21"/>
+    </row>
+    <row r="22" spans="2:11" ht="18" x14ac:dyDescent="0.35">
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="8"/>
+      <c r="I22" s="21"/>
+      <c r="J22" s="21"/>
+      <c r="K22" s="21"/>
+    </row>
+    <row r="23" spans="2:11" ht="18" x14ac:dyDescent="0.35">
+      <c r="B23" s="21"/>
+      <c r="C23" s="21"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="21"/>
+      <c r="G23" s="21"/>
+      <c r="H23" s="21"/>
+      <c r="I23" s="21"/>
+      <c r="J23" s="21"/>
+      <c r="K23" s="21"/>
+    </row>
+    <row r="24" spans="2:11" ht="18" x14ac:dyDescent="0.35">
+      <c r="B24" s="21"/>
+      <c r="C24" s="21"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="21"/>
+      <c r="G24" s="21"/>
+      <c r="H24" s="21"/>
+      <c r="I24" s="21"/>
+      <c r="J24" s="21"/>
+      <c r="K24" s="21"/>
+    </row>
+    <row r="25" spans="2:11" ht="18" x14ac:dyDescent="0.35">
+      <c r="B25" s="21"/>
+      <c r="C25" s="21"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="21"/>
+      <c r="G25" s="21"/>
+      <c r="H25" s="21"/>
+      <c r="I25" s="21"/>
+      <c r="J25" s="21"/>
+      <c r="K25" s="21"/>
+    </row>
+    <row r="26" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B26" s="21"/>
+      <c r="C26" s="21"/>
+      <c r="D26" s="21"/>
+      <c r="E26" s="21"/>
+      <c r="F26" s="21"/>
+      <c r="G26" s="21"/>
+      <c r="H26" s="21"/>
+      <c r="I26" s="21"/>
+      <c r="J26" s="21"/>
+      <c r="K26" s="21"/>
+    </row>
+    <row r="27" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B27" s="21"/>
+      <c r="C27" s="21"/>
+      <c r="D27" s="21"/>
+      <c r="E27" s="21"/>
+      <c r="F27" s="21"/>
+      <c r="G27" s="21"/>
+      <c r="H27" s="21"/>
+      <c r="I27" s="21"/>
+      <c r="J27" s="21"/>
+      <c r="K27" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -1331,18 +1512,18 @@
         <f>$B2*C2</f>
         <v>3</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="6" t="s">
         <v>13</v>
       </c>
       <c r="K2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="L2" s="7" t="s">
+      <c r="L2" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
+      <c r="M2" s="18"/>
+      <c r="N2" s="18"/>
+      <c r="O2" s="18"/>
     </row>
     <row r="3" spans="2:15" ht="25.8" x14ac:dyDescent="0.3">
       <c r="B3" s="1">
@@ -1358,10 +1539,10 @@
       <c r="K3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="L3" s="7"/>
-      <c r="M3" s="7"/>
-      <c r="N3" s="7"/>
-      <c r="O3" s="7"/>
+      <c r="L3" s="18"/>
+      <c r="M3" s="18"/>
+      <c r="N3" s="18"/>
+      <c r="O3" s="18"/>
     </row>
     <row r="4" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B4" s="1">
@@ -1389,12 +1570,12 @@
       <c r="K5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="L5" s="7" t="s">
+      <c r="L5" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="M5" s="7"/>
-      <c r="N5" s="7"/>
-      <c r="O5" s="7"/>
+      <c r="M5" s="18"/>
+      <c r="N5" s="18"/>
+      <c r="O5" s="18"/>
     </row>
     <row r="6" spans="2:15" ht="25.8" x14ac:dyDescent="0.3">
       <c r="B6" s="1">
@@ -1410,10 +1591,10 @@
       <c r="K6" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="L6" s="7"/>
-      <c r="M6" s="7"/>
-      <c r="N6" s="7"/>
-      <c r="O6" s="7"/>
+      <c r="L6" s="18"/>
+      <c r="M6" s="18"/>
+      <c r="N6" s="18"/>
+      <c r="O6" s="18"/>
     </row>
     <row r="7" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B7" s="1">
@@ -1426,12 +1607,12 @@
         <f t="shared" si="0"/>
         <v>108</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="F7" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="6"/>
+      <c r="G7" s="19"/>
+      <c r="H7" s="19"/>
+      <c r="I7" s="19"/>
     </row>
     <row r="8" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B8" s="1">
@@ -1444,10 +1625,10 @@
         <f t="shared" si="0"/>
         <v>147</v>
       </c>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="19"/>
+      <c r="H8" s="19"/>
+      <c r="I8" s="19"/>
     </row>
     <row r="9" spans="2:15" ht="25.8" x14ac:dyDescent="0.5">
       <c r="B9" s="1">
@@ -1460,19 +1641,19 @@
         <f t="shared" si="0"/>
         <v>192</v>
       </c>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6"/>
-      <c r="K9" s="17" t="s">
+      <c r="F9" s="19"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="19"/>
+      <c r="I9" s="19"/>
+      <c r="K9" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="L9" s="18" t="s">
+      <c r="L9" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="M9" s="18"/>
-      <c r="N9" s="18"/>
-      <c r="O9" s="18"/>
+      <c r="M9" s="20"/>
+      <c r="N9" s="20"/>
+      <c r="O9" s="20"/>
     </row>
     <row r="10" spans="2:15" ht="25.8" x14ac:dyDescent="0.3">
       <c r="B10" s="1">
@@ -1485,13 +1666,13 @@
         <f t="shared" si="0"/>
         <v>243</v>
       </c>
-      <c r="K10" s="19" t="s">
+      <c r="K10" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="L10" s="18"/>
-      <c r="M10" s="18"/>
-      <c r="N10" s="18"/>
-      <c r="O10" s="18"/>
+      <c r="L10" s="20"/>
+      <c r="M10" s="20"/>
+      <c r="N10" s="20"/>
+      <c r="O10" s="20"/>
     </row>
     <row r="11" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B11" s="1">
@@ -1509,21 +1690,21 @@
       <c r="K12" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="L12" s="7" t="s">
+      <c r="L12" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="M12" s="7"/>
-      <c r="N12" s="7"/>
-      <c r="O12" s="7"/>
+      <c r="M12" s="18"/>
+      <c r="N12" s="18"/>
+      <c r="O12" s="18"/>
     </row>
     <row r="13" spans="2:15" ht="25.8" x14ac:dyDescent="0.3">
       <c r="K13" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="L13" s="7"/>
-      <c r="M13" s="7"/>
-      <c r="N13" s="7"/>
-      <c r="O13" s="7"/>
+      <c r="L13" s="18"/>
+      <c r="M13" s="18"/>
+      <c r="N13" s="18"/>
+      <c r="O13" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -1569,19 +1750,19 @@
       <c r="F2" s="3">
         <v>6</v>
       </c>
-      <c r="G2" s="20"/>
-      <c r="H2" s="8" t="s">
+      <c r="G2" s="13"/>
+      <c r="H2" s="6" t="s">
         <v>13</v>
       </c>
       <c r="L2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="M2" s="7" t="s">
+      <c r="M2" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7"/>
+      <c r="N2" s="18"/>
+      <c r="O2" s="18"/>
+      <c r="P2" s="18"/>
     </row>
     <row r="3" spans="1:16" ht="25.8" x14ac:dyDescent="0.4">
       <c r="A3" s="3">
@@ -1602,14 +1783,14 @@
       <c r="F3" s="3">
         <v>30</v>
       </c>
-      <c r="G3" s="20"/>
+      <c r="G3" s="13"/>
       <c r="L3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="M3" s="7"/>
-      <c r="N3" s="7"/>
-      <c r="O3" s="7"/>
-      <c r="P3" s="7"/>
+      <c r="M3" s="18"/>
+      <c r="N3" s="18"/>
+      <c r="O3" s="18"/>
+      <c r="P3" s="18"/>
     </row>
     <row r="4" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A4" s="3">
@@ -1636,85 +1817,279 @@
         <f t="shared" si="0"/>
         <v>180</v>
       </c>
-      <c r="G4" s="20"/>
+      <c r="G4" s="13"/>
     </row>
     <row r="5" spans="1:16" ht="25.8" x14ac:dyDescent="0.5">
+      <c r="A5" s="3">
+        <f t="shared" ref="A5:F12" si="1">A$2*A4</f>
+        <v>5</v>
+      </c>
+      <c r="B5" s="3">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="C5" s="3">
+        <f t="shared" si="1"/>
+        <v>135</v>
+      </c>
+      <c r="D5" s="3">
+        <f t="shared" si="1"/>
+        <v>320</v>
+      </c>
+      <c r="E5" s="3">
+        <f t="shared" si="1"/>
+        <v>625</v>
+      </c>
+      <c r="F5" s="3">
+        <f t="shared" si="1"/>
+        <v>1080</v>
+      </c>
       <c r="L5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="M5" s="7" t="s">
+      <c r="M5" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="N5" s="7"/>
-      <c r="O5" s="7"/>
-      <c r="P5" s="7"/>
-    </row>
-    <row r="6" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="G6" s="6" t="s">
+      <c r="N5" s="18"/>
+      <c r="O5" s="18"/>
+      <c r="P5" s="18"/>
+    </row>
+    <row r="6" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="3">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="B6" s="3">
+        <f t="shared" si="1"/>
+        <v>80</v>
+      </c>
+      <c r="C6" s="3">
+        <f t="shared" si="1"/>
+        <v>405</v>
+      </c>
+      <c r="D6" s="3">
+        <f t="shared" si="1"/>
+        <v>1280</v>
+      </c>
+      <c r="E6" s="3">
+        <f t="shared" si="1"/>
+        <v>3125</v>
+      </c>
+      <c r="F6" s="3">
+        <f t="shared" si="1"/>
+        <v>6480</v>
+      </c>
+      <c r="G6" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="H6" s="6"/>
-      <c r="I6" s="6"/>
-      <c r="J6" s="6"/>
+      <c r="H6" s="19"/>
+      <c r="I6" s="19"/>
+      <c r="J6" s="19"/>
       <c r="L6" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="M6" s="7"/>
-      <c r="N6" s="7"/>
-      <c r="O6" s="7"/>
-      <c r="P6" s="7"/>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="6"/>
-      <c r="J7" s="6"/>
-    </row>
-    <row r="8" spans="1:16" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6"/>
-      <c r="J8" s="6"/>
+      <c r="M6" s="18"/>
+      <c r="N6" s="18"/>
+      <c r="O6" s="18"/>
+      <c r="P6" s="18"/>
+    </row>
+    <row r="7" spans="1:16" ht="21" x14ac:dyDescent="0.4">
+      <c r="A7" s="3">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="B7" s="3">
+        <f t="shared" si="1"/>
+        <v>160</v>
+      </c>
+      <c r="C7" s="3">
+        <f t="shared" si="1"/>
+        <v>1215</v>
+      </c>
+      <c r="D7" s="3">
+        <f t="shared" si="1"/>
+        <v>5120</v>
+      </c>
+      <c r="E7" s="3">
+        <f t="shared" si="1"/>
+        <v>15625</v>
+      </c>
+      <c r="F7" s="3">
+        <f t="shared" si="1"/>
+        <v>38880</v>
+      </c>
+      <c r="G7" s="19"/>
+      <c r="H7" s="19"/>
+      <c r="I7" s="19"/>
+      <c r="J7" s="19"/>
+    </row>
+    <row r="8" spans="1:16" ht="61.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="3">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="B8" s="3">
+        <f t="shared" si="1"/>
+        <v>320</v>
+      </c>
+      <c r="C8" s="3">
+        <f t="shared" si="1"/>
+        <v>3645</v>
+      </c>
+      <c r="D8" s="3">
+        <f t="shared" si="1"/>
+        <v>20480</v>
+      </c>
+      <c r="E8" s="3">
+        <f t="shared" si="1"/>
+        <v>78125</v>
+      </c>
+      <c r="F8" s="3">
+        <f t="shared" si="1"/>
+        <v>233280</v>
+      </c>
+      <c r="G8" s="19"/>
+      <c r="H8" s="19"/>
+      <c r="I8" s="19"/>
+      <c r="J8" s="19"/>
     </row>
     <row r="9" spans="1:16" ht="25.8" x14ac:dyDescent="0.5">
+      <c r="A9" s="3">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="B9" s="3">
+        <f t="shared" si="1"/>
+        <v>640</v>
+      </c>
+      <c r="C9" s="3">
+        <f t="shared" si="1"/>
+        <v>10935</v>
+      </c>
+      <c r="D9" s="3">
+        <f t="shared" si="1"/>
+        <v>81920</v>
+      </c>
+      <c r="E9" s="3">
+        <f t="shared" si="1"/>
+        <v>390625</v>
+      </c>
+      <c r="F9" s="3">
+        <f t="shared" si="1"/>
+        <v>1399680</v>
+      </c>
       <c r="L9" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="M9" s="7" t="s">
+      <c r="M9" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="N9" s="7"/>
-      <c r="O9" s="7"/>
-      <c r="P9" s="7"/>
-    </row>
-    <row r="10" spans="1:16" ht="25.8" x14ac:dyDescent="0.3">
+      <c r="N9" s="18"/>
+      <c r="O9" s="18"/>
+      <c r="P9" s="18"/>
+    </row>
+    <row r="10" spans="1:16" ht="25.8" x14ac:dyDescent="0.4">
+      <c r="A10" s="3">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="B10" s="3">
+        <f t="shared" si="1"/>
+        <v>1280</v>
+      </c>
+      <c r="C10" s="3">
+        <f t="shared" si="1"/>
+        <v>32805</v>
+      </c>
+      <c r="D10" s="3">
+        <f t="shared" si="1"/>
+        <v>327680</v>
+      </c>
+      <c r="E10" s="3">
+        <f t="shared" si="1"/>
+        <v>1953125</v>
+      </c>
+      <c r="F10" s="3">
+        <f t="shared" si="1"/>
+        <v>8398080</v>
+      </c>
       <c r="L10" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="M10" s="7"/>
-      <c r="N10" s="7"/>
-      <c r="O10" s="7"/>
-      <c r="P10" s="7"/>
+      <c r="M10" s="18"/>
+      <c r="N10" s="18"/>
+      <c r="O10" s="18"/>
+      <c r="P10" s="18"/>
+    </row>
+    <row r="11" spans="1:16" ht="21" x14ac:dyDescent="0.4">
+      <c r="A11" s="3">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="B11" s="3">
+        <f t="shared" si="1"/>
+        <v>2560</v>
+      </c>
+      <c r="C11" s="3">
+        <f t="shared" si="1"/>
+        <v>98415</v>
+      </c>
+      <c r="D11" s="3">
+        <f t="shared" si="1"/>
+        <v>1310720</v>
+      </c>
+      <c r="E11" s="3">
+        <f t="shared" si="1"/>
+        <v>9765625</v>
+      </c>
+      <c r="F11" s="3">
+        <f t="shared" si="1"/>
+        <v>50388480</v>
+      </c>
     </row>
     <row r="12" spans="1:16" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="L12" s="17" t="s">
+      <c r="A12" s="3">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="B12" s="3">
+        <f t="shared" si="1"/>
+        <v>5120</v>
+      </c>
+      <c r="C12" s="3">
+        <f t="shared" si="1"/>
+        <v>295245</v>
+      </c>
+      <c r="D12" s="3">
+        <f t="shared" si="1"/>
+        <v>5242880</v>
+      </c>
+      <c r="E12" s="3">
+        <f t="shared" si="1"/>
+        <v>48828125</v>
+      </c>
+      <c r="F12" s="3">
+        <f t="shared" si="1"/>
+        <v>302330880</v>
+      </c>
+      <c r="L12" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="M12" s="18" t="s">
+      <c r="M12" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="N12" s="18"/>
-      <c r="O12" s="18"/>
-      <c r="P12" s="18"/>
+      <c r="N12" s="20"/>
+      <c r="O12" s="20"/>
+      <c r="P12" s="20"/>
     </row>
     <row r="13" spans="1:16" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="L13" s="19" t="s">
+      <c r="L13" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="M13" s="18"/>
-      <c r="N13" s="18"/>
-      <c r="O13" s="18"/>
-      <c r="P13" s="18"/>
+      <c r="M13" s="20"/>
+      <c r="N13" s="20"/>
+      <c r="O13" s="20"/>
+      <c r="P13" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="5">
